--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/39.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/39.xlsx
@@ -426,13 +426,13 @@
         <v>-23.16249147386504</v>
       </c>
       <c r="E2">
-        <v>-10.67142998800767</v>
+        <v>-3.809141214163343</v>
       </c>
       <c r="F2">
-        <v>1.973759975444305</v>
+        <v>2.961057948144924</v>
       </c>
       <c r="G2">
-        <v>-16.95982578718806</v>
+        <v>-15.91837888383624</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.38350279368097</v>
       </c>
       <c r="E3">
-        <v>-8.647237852512735</v>
+        <v>-4.615175702029441</v>
       </c>
       <c r="F3">
-        <v>2.213035556477748</v>
+        <v>2.991015026899765</v>
       </c>
       <c r="G3">
-        <v>-16.16094055305199</v>
+        <v>-14.70265041993236</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-21.2836707213344</v>
       </c>
       <c r="E4">
-        <v>-12.75257511039998</v>
+        <v>-4.526832743939014</v>
       </c>
       <c r="F4">
-        <v>1.798141115846393</v>
+        <v>2.541680383129618</v>
       </c>
       <c r="G4">
-        <v>-16.3944037773677</v>
+        <v>-14.49399318534911</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.97631681071188</v>
       </c>
       <c r="E5">
-        <v>-12.40966521736551</v>
+        <v>-5.34737439896274</v>
       </c>
       <c r="F5">
-        <v>1.913098630537297</v>
+        <v>3.145263664240256</v>
       </c>
       <c r="G5">
-        <v>-16.03424633953444</v>
+        <v>-14.34045399057344</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.47548352498104</v>
       </c>
       <c r="E6">
-        <v>-12.84926187004199</v>
+        <v>-6.132123678789092</v>
       </c>
       <c r="F6">
-        <v>2.076957986485068</v>
+        <v>3.21360563170602</v>
       </c>
       <c r="G6">
-        <v>-15.04603512914001</v>
+        <v>-13.34092128625965</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.85387256774426</v>
       </c>
       <c r="E7">
-        <v>-11.95216822387902</v>
+        <v>-7.27841000444177</v>
       </c>
       <c r="F7">
-        <v>2.229201974710783</v>
+        <v>3.027993347760735</v>
       </c>
       <c r="G7">
-        <v>-15.18446202885002</v>
+        <v>-13.11823260487146</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.16213999999509</v>
       </c>
       <c r="E8">
-        <v>-14.26379996195401</v>
+        <v>-7.843695291441533</v>
       </c>
       <c r="F8">
-        <v>2.148692946832699</v>
+        <v>3.337388572706351</v>
       </c>
       <c r="G8">
-        <v>-13.96150441317335</v>
+        <v>-12.33063884109195</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.45347847861277</v>
       </c>
       <c r="E9">
-        <v>-13.50886243301728</v>
+        <v>-7.737439532907119</v>
       </c>
       <c r="F9">
-        <v>2.083758882862051</v>
+        <v>3.496943731629174</v>
       </c>
       <c r="G9">
-        <v>-13.54982001471758</v>
+        <v>-11.93773222310777</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.7805245418906</v>
       </c>
       <c r="E10">
-        <v>-13.71256498886615</v>
+        <v>-8.358444303040782</v>
       </c>
       <c r="F10">
-        <v>2.716581876556706</v>
+        <v>3.552081522694315</v>
       </c>
       <c r="G10">
-        <v>-12.52203122169417</v>
+        <v>-11.2802396945372</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.16882949578893</v>
       </c>
       <c r="E11">
-        <v>-15.17296284022693</v>
+        <v>-9.865765135949481</v>
       </c>
       <c r="F11">
-        <v>2.229993893947859</v>
+        <v>3.622322108247297</v>
       </c>
       <c r="G11">
-        <v>-12.8451526367579</v>
+        <v>-10.73316860844778</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.663532545649026</v>
       </c>
       <c r="E12">
-        <v>-15.26446639213555</v>
+        <v>-9.616684593165537</v>
       </c>
       <c r="F12">
-        <v>2.94125831048321</v>
+        <v>3.795628166056592</v>
       </c>
       <c r="G12">
-        <v>-12.48426680118372</v>
+        <v>-9.279740987129102</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.271568643582845</v>
       </c>
       <c r="E13">
-        <v>-16.16743267911183</v>
+        <v>-10.18081944062832</v>
       </c>
       <c r="F13">
-        <v>3.152861450058733</v>
+        <v>3.801713352997557</v>
       </c>
       <c r="G13">
-        <v>-10.72834786856029</v>
+        <v>-9.2821507043867</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.028181188390388</v>
       </c>
       <c r="E14">
-        <v>-18.00801549514741</v>
+        <v>-11.90698128466489</v>
       </c>
       <c r="F14">
-        <v>3.274170885994304</v>
+        <v>3.968500159346821</v>
       </c>
       <c r="G14">
-        <v>-11.49395002527656</v>
+        <v>-8.25947374927269</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.934710407072679</v>
       </c>
       <c r="E15">
-        <v>-19.4624410286231</v>
+        <v>-11.94584703624263</v>
       </c>
       <c r="F15">
-        <v>3.174268120481877</v>
+        <v>3.975967063115656</v>
       </c>
       <c r="G15">
-        <v>-9.895853213930518</v>
+        <v>-7.574212035858753</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.998468062766487</v>
       </c>
       <c r="E16">
-        <v>-17.77839274742029</v>
+        <v>-12.41273028732323</v>
       </c>
       <c r="F16">
-        <v>3.59589056115877</v>
+        <v>4.375019805535873</v>
       </c>
       <c r="G16">
-        <v>-10.2732206801084</v>
+        <v>-7.023384088302716</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.211317530994989</v>
       </c>
       <c r="E17">
-        <v>-18.85360101445986</v>
+        <v>-13.65688703784549</v>
       </c>
       <c r="F17">
-        <v>3.302211122579067</v>
+        <v>4.24484186818593</v>
       </c>
       <c r="G17">
-        <v>-8.924063587014192</v>
+        <v>-6.38642245519667</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.555635205015909</v>
       </c>
       <c r="E18">
-        <v>-21.19700481916979</v>
+        <v>-15.1585553501411</v>
       </c>
       <c r="F18">
-        <v>4.018034873299426</v>
+        <v>4.606512046452611</v>
       </c>
       <c r="G18">
-        <v>-8.332368349001165</v>
+        <v>-5.738346882366255</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.017768039041921</v>
       </c>
       <c r="E19">
-        <v>-21.05493176617005</v>
+        <v>-15.75345718709822</v>
       </c>
       <c r="F19">
-        <v>4.309608601941212</v>
+        <v>4.711144789835022</v>
       </c>
       <c r="G19">
-        <v>-7.208608584808431</v>
+        <v>-5.185221479570039</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.570645600645035</v>
       </c>
       <c r="E20">
-        <v>-19.51492931334628</v>
+        <v>-16.22991359028255</v>
       </c>
       <c r="F20">
-        <v>4.613765231431524</v>
+        <v>5.061189659970815</v>
       </c>
       <c r="G20">
-        <v>-7.360961196167437</v>
+        <v>-4.490061128038895</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.203318784020717</v>
       </c>
       <c r="E21">
-        <v>-21.47086342071766</v>
+        <v>-17.03840262604162</v>
       </c>
       <c r="F21">
-        <v>4.15011308547139</v>
+        <v>4.886539990234179</v>
       </c>
       <c r="G21">
-        <v>-7.145420733469716</v>
+        <v>-4.438258733862026</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.8920640409641184</v>
       </c>
       <c r="E22">
-        <v>-21.60050175901086</v>
+        <v>-16.64501044935386</v>
       </c>
       <c r="F22">
-        <v>4.616775518573298</v>
+        <v>5.062838111102386</v>
       </c>
       <c r="G22">
-        <v>-7.502769010122938</v>
+        <v>-4.181186546208874</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.6332929985643125</v>
       </c>
       <c r="E23">
-        <v>-22.57409340456584</v>
+        <v>-16.94397936657164</v>
       </c>
       <c r="F23">
-        <v>4.95882498653727</v>
+        <v>5.371207817203336</v>
       </c>
       <c r="G23">
-        <v>-6.752649874204269</v>
+        <v>-3.829809042435528</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.4173261393306817</v>
       </c>
       <c r="E24">
-        <v>-23.24809730441564</v>
+        <v>-17.38980168302404</v>
       </c>
       <c r="F24">
-        <v>4.724228024594838</v>
+        <v>5.279070167724752</v>
       </c>
       <c r="G24">
-        <v>-6.98294104384178</v>
+        <v>-4.097065744738613</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.2463484539554143</v>
       </c>
       <c r="E25">
-        <v>-24.72820214351274</v>
+        <v>-17.98314606573434</v>
       </c>
       <c r="F25">
-        <v>5.281704376065655</v>
+        <v>5.043633241235883</v>
       </c>
       <c r="G25">
-        <v>-6.733534002308137</v>
+        <v>-3.983279052479531</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.1235122664912185</v>
       </c>
       <c r="E26">
-        <v>-23.28866587263656</v>
+        <v>-18.74274349777754</v>
       </c>
       <c r="F26">
-        <v>4.710435707338227</v>
+        <v>5.204845134964305</v>
       </c>
       <c r="G26">
-        <v>-7.718900806470547</v>
+        <v>-4.037243143177842</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.05335755229245055</v>
       </c>
       <c r="E27">
-        <v>-22.01592672177683</v>
+        <v>-17.51610914583472</v>
       </c>
       <c r="F27">
-        <v>5.053379812097221</v>
+        <v>5.164057980785263</v>
       </c>
       <c r="G27">
-        <v>-7.406424702477085</v>
+        <v>-3.853976705115463</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.04103687118663164</v>
       </c>
       <c r="E28">
-        <v>-21.55597933360869</v>
+        <v>-18.58396622882934</v>
       </c>
       <c r="F28">
-        <v>4.198178275651428</v>
+        <v>5.492258802509233</v>
       </c>
       <c r="G28">
-        <v>-6.914385501623737</v>
+        <v>-3.976224820594343</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.08453310463931443</v>
       </c>
       <c r="E29">
-        <v>-23.00969882115916</v>
+        <v>-18.54956517942578</v>
       </c>
       <c r="F29">
-        <v>5.338767292974902</v>
+        <v>5.196377563372889</v>
       </c>
       <c r="G29">
-        <v>-7.806416881281551</v>
+        <v>-4.486265105403416</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.1826037107318601</v>
       </c>
       <c r="E30">
-        <v>-22.8179076753899</v>
+        <v>-18.56251904554792</v>
       </c>
       <c r="F30">
-        <v>4.73662371441033</v>
+        <v>5.238032846590065</v>
       </c>
       <c r="G30">
-        <v>-7.572149547631773</v>
+        <v>-4.165984180454821</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.324047361342622</v>
       </c>
       <c r="E31">
-        <v>-21.0708302591215</v>
+        <v>-19.12498845526945</v>
       </c>
       <c r="F31">
-        <v>4.679294063197381</v>
+        <v>5.344537700302803</v>
       </c>
       <c r="G31">
-        <v>-7.869218342420781</v>
+        <v>-4.385148356645008</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.4996128462230628</v>
       </c>
       <c r="E32">
-        <v>-22.67475478744571</v>
+        <v>-17.86747497712654</v>
       </c>
       <c r="F32">
-        <v>4.549439189134531</v>
+        <v>5.231349578384278</v>
       </c>
       <c r="G32">
-        <v>-6.771314087286138</v>
+        <v>-4.175189665883086</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.6963552333208612</v>
       </c>
       <c r="E33">
-        <v>-22.47982381391488</v>
+        <v>-18.03340822918742</v>
       </c>
       <c r="F33">
-        <v>4.188004267210245</v>
+        <v>5.457140994834951</v>
       </c>
       <c r="G33">
-        <v>-7.982685218467451</v>
+        <v>-4.455680232518525</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.9086619879870025</v>
       </c>
       <c r="E34">
-        <v>-22.258872971434</v>
+        <v>-17.77009047798196</v>
       </c>
       <c r="F34">
-        <v>5.529863369126719</v>
+        <v>5.829795324862753</v>
       </c>
       <c r="G34">
-        <v>-7.076998339225819</v>
+        <v>-4.732949140328529</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.133019538122876</v>
       </c>
       <c r="E35">
-        <v>-20.51493538292717</v>
+        <v>-17.18318772603647</v>
       </c>
       <c r="F35">
-        <v>5.500653477769204</v>
+        <v>5.973924626010645</v>
       </c>
       <c r="G35">
-        <v>-8.427917684919024</v>
+        <v>-4.85644258097737</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.367237142259559</v>
       </c>
       <c r="E36">
-        <v>-21.46156438056137</v>
+        <v>-16.91216161461213</v>
       </c>
       <c r="F36">
-        <v>5.573092550409214</v>
+        <v>5.632150176024402</v>
       </c>
       <c r="G36">
-        <v>-8.30589148273039</v>
+        <v>-4.63778749998245</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.60961522977131</v>
       </c>
       <c r="E37">
-        <v>-21.45415089834655</v>
+        <v>-16.58063982703034</v>
       </c>
       <c r="F37">
-        <v>4.888996927950882</v>
+        <v>6.016419873774259</v>
       </c>
       <c r="G37">
-        <v>-7.397422855126925</v>
+        <v>-4.868214428338699</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.855288730150831</v>
       </c>
       <c r="E38">
-        <v>-20.0049833304081</v>
+        <v>-16.2783151150621</v>
       </c>
       <c r="F38">
-        <v>5.137863346773938</v>
+        <v>6.068340285846927</v>
       </c>
       <c r="G38">
-        <v>-7.852624449799665</v>
+        <v>-4.637134813834671</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.102457388091722</v>
       </c>
       <c r="E39">
-        <v>-20.27600528862111</v>
+        <v>-16.6343450026717</v>
       </c>
       <c r="F39">
-        <v>6.160960045153939</v>
+        <v>6.238205305464994</v>
       </c>
       <c r="G39">
-        <v>-8.511231766310631</v>
+        <v>-4.415137979763126</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.344066795513312</v>
       </c>
       <c r="E40">
-        <v>-18.52001923406095</v>
+        <v>-16.22431090820535</v>
       </c>
       <c r="F40">
-        <v>5.242083563189754</v>
+        <v>6.520189853051973</v>
       </c>
       <c r="G40">
-        <v>-8.051762909603717</v>
+        <v>-4.634847801572856</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.578054796867999</v>
       </c>
       <c r="E41">
-        <v>-20.05783294451654</v>
+        <v>-15.48611082090768</v>
       </c>
       <c r="F41">
-        <v>5.26243986374615</v>
+        <v>6.499286830009731</v>
       </c>
       <c r="G41">
-        <v>-9.082183333174969</v>
+        <v>-5.358031885545009</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.797486825383573</v>
       </c>
       <c r="E42">
-        <v>-19.11365018835267</v>
+        <v>-15.60181513520608</v>
       </c>
       <c r="F42">
-        <v>5.406009188529748</v>
+        <v>6.693524075352964</v>
       </c>
       <c r="G42">
-        <v>-8.620642850635006</v>
+        <v>-5.015405597641075</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.999417759154441</v>
       </c>
       <c r="E43">
-        <v>-18.36533287826771</v>
+        <v>-13.88470313864632</v>
       </c>
       <c r="F43">
-        <v>4.995722127392765</v>
+        <v>6.833195103138989</v>
       </c>
       <c r="G43">
-        <v>-9.154422636011073</v>
+        <v>-5.344121838363558</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.179505826908704</v>
       </c>
       <c r="E44">
-        <v>-18.56529339071291</v>
+        <v>-13.8426477207711</v>
       </c>
       <c r="F44">
-        <v>5.218574496298305</v>
+        <v>6.478186655525621</v>
       </c>
       <c r="G44">
-        <v>-9.180701085692924</v>
+        <v>-5.690873102721451</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.335850564784322</v>
       </c>
       <c r="E45">
-        <v>-16.37861932176803</v>
+        <v>-13.60445274486954</v>
       </c>
       <c r="F45">
-        <v>4.893697084594367</v>
+        <v>6.081464938976882</v>
       </c>
       <c r="G45">
-        <v>-9.335152735703186</v>
+        <v>-5.418118172309482</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.470240623138667</v>
       </c>
       <c r="E46">
-        <v>-16.91947957296648</v>
+        <v>-13.11429489752459</v>
       </c>
       <c r="F46">
-        <v>4.962027454916492</v>
+        <v>6.6612227168482</v>
       </c>
       <c r="G46">
-        <v>-9.345240652803248</v>
+        <v>-6.051876421802231</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.582814597011103</v>
       </c>
       <c r="E47">
-        <v>-15.98278090360995</v>
+        <v>-12.44679492660948</v>
       </c>
       <c r="F47">
-        <v>5.322055808990824</v>
+        <v>6.592527864868843</v>
       </c>
       <c r="G47">
-        <v>-9.149886467284015</v>
+        <v>-5.984482660927234</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.682208885860142</v>
       </c>
       <c r="E48">
-        <v>-15.28011153919618</v>
+        <v>-11.75936784775783</v>
       </c>
       <c r="F48">
-        <v>5.170809175118079</v>
+        <v>6.549171115006317</v>
       </c>
       <c r="G48">
-        <v>-9.46128041764446</v>
+        <v>-5.385361159924783</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.770009053121099</v>
       </c>
       <c r="E49">
-        <v>-15.94712973759762</v>
+        <v>-11.36056818992514</v>
       </c>
       <c r="F49">
-        <v>4.693074783310355</v>
+        <v>6.569449549026849</v>
       </c>
       <c r="G49">
-        <v>-9.704720602415115</v>
+        <v>-5.799234667720199</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.858873719092164</v>
       </c>
       <c r="E50">
-        <v>-15.35955831862883</v>
+        <v>-11.35874077694222</v>
       </c>
       <c r="F50">
-        <v>4.822276903859799</v>
+        <v>6.301466067281986</v>
       </c>
       <c r="G50">
-        <v>-9.135818470054801</v>
+        <v>-6.285122954316884</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.953076858912001</v>
       </c>
       <c r="E51">
-        <v>-16.48346714166333</v>
+        <v>-10.30915367056553</v>
       </c>
       <c r="F51">
-        <v>5.241465601107266</v>
+        <v>6.243521767456161</v>
       </c>
       <c r="G51">
-        <v>-8.707741206311432</v>
+        <v>-6.227161813649578</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.065343464699282</v>
       </c>
       <c r="E52">
-        <v>-14.71613866697507</v>
+        <v>-10.76097322417097</v>
       </c>
       <c r="F52">
-        <v>5.046978188808387</v>
+        <v>6.322983738937106</v>
       </c>
       <c r="G52">
-        <v>-9.307566302981188</v>
+        <v>-6.437439015251615</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.203058819093735</v>
       </c>
       <c r="E53">
-        <v>-13.15237569216195</v>
+        <v>-9.690105062965857</v>
       </c>
       <c r="F53">
-        <v>4.774576195336992</v>
+        <v>5.907035614969391</v>
       </c>
       <c r="G53">
-        <v>-9.652540955644829</v>
+        <v>-6.430173313054547</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.373502092464797</v>
       </c>
       <c r="E54">
-        <v>-13.33168228468877</v>
+        <v>-9.723405511368332</v>
       </c>
       <c r="F54">
-        <v>5.177580250268562</v>
+        <v>6.361738079509678</v>
       </c>
       <c r="G54">
-        <v>-9.391909017741694</v>
+        <v>-6.801470798058087</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.582742805775534</v>
       </c>
       <c r="E55">
-        <v>-14.16386954426732</v>
+        <v>-9.653872447368053</v>
       </c>
       <c r="F55">
-        <v>4.768437992882247</v>
+        <v>6.143980170131355</v>
       </c>
       <c r="G55">
-        <v>-9.441955686181039</v>
+        <v>-7.084929781293621</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.826781841014594</v>
       </c>
       <c r="E56">
-        <v>-11.72325982849977</v>
+        <v>-9.03165493952754</v>
       </c>
       <c r="F56">
-        <v>4.910335672246998</v>
+        <v>5.895208185192219</v>
       </c>
       <c r="G56">
-        <v>-9.505819720368853</v>
+        <v>-6.718122776986796</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.108849316757502</v>
       </c>
       <c r="E57">
-        <v>-12.98884714945815</v>
+        <v>-8.965494283123022</v>
       </c>
       <c r="F57">
-        <v>4.945470047269335</v>
+        <v>6.091738351506402</v>
       </c>
       <c r="G57">
-        <v>-10.25866316826835</v>
+        <v>-6.974325586691107</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.415038267880194</v>
       </c>
       <c r="E58">
-        <v>-13.83983184349287</v>
+        <v>-8.07483811451354</v>
       </c>
       <c r="F58">
-        <v>4.825022113432676</v>
+        <v>5.840501145176535</v>
       </c>
       <c r="G58">
-        <v>-9.685205286596542</v>
+        <v>-7.005672796996604</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.745835366970391</v>
       </c>
       <c r="E59">
-        <v>-12.77857836650473</v>
+        <v>-8.596311175247687</v>
       </c>
       <c r="F59">
-        <v>4.76450324771895</v>
+        <v>5.571748938481874</v>
       </c>
       <c r="G59">
-        <v>-10.52124011089186</v>
+        <v>-7.668031753485</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.085966400890434</v>
       </c>
       <c r="E60">
-        <v>-11.51911287903915</v>
+        <v>-7.28036201376444</v>
       </c>
       <c r="F60">
-        <v>4.612602203597993</v>
+        <v>5.785141351647443</v>
       </c>
       <c r="G60">
-        <v>-10.78955024863746</v>
+        <v>-6.909863691991928</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.432559031203776</v>
       </c>
       <c r="E61">
-        <v>-12.80356823904622</v>
+        <v>-7.167776761170987</v>
       </c>
       <c r="F61">
-        <v>4.693583400895673</v>
+        <v>6.207012302545175</v>
       </c>
       <c r="G61">
-        <v>-10.37468596326972</v>
+        <v>-7.861414826837944</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.775074723296434</v>
       </c>
       <c r="E62">
-        <v>-10.47113721865649</v>
+        <v>-8.080428336956761</v>
       </c>
       <c r="F62">
-        <v>4.781932097873852</v>
+        <v>5.908074387692501</v>
       </c>
       <c r="G62">
-        <v>-9.712633769270779</v>
+        <v>-7.973242155281395</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.107924272556255</v>
       </c>
       <c r="E63">
-        <v>-10.62282910908453</v>
+        <v>-6.874651412287238</v>
       </c>
       <c r="F63">
-        <v>3.990720286559515</v>
+        <v>5.801930702167383</v>
       </c>
       <c r="G63">
-        <v>-11.63168246692533</v>
+        <v>-8.118184168118527</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.428671967127291</v>
       </c>
       <c r="E64">
-        <v>-10.56884982149573</v>
+        <v>-7.001324357694509</v>
       </c>
       <c r="F64">
-        <v>4.543291046270953</v>
+        <v>6.254230901239553</v>
       </c>
       <c r="G64">
-        <v>-10.23303871010657</v>
+        <v>-8.13723477139988</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.729376962582009</v>
       </c>
       <c r="E65">
-        <v>-13.23745007293974</v>
+        <v>-7.01641297443761</v>
       </c>
       <c r="F65">
-        <v>4.99284769250505</v>
+        <v>5.839939512077436</v>
       </c>
       <c r="G65">
-        <v>-10.77130636543476</v>
+        <v>-8.310334970024464</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.016248156427395</v>
       </c>
       <c r="E66">
-        <v>-12.51306356650844</v>
+        <v>-7.234792979108421</v>
       </c>
       <c r="F66">
-        <v>4.329005653045166</v>
+        <v>5.570612418405233</v>
       </c>
       <c r="G66">
-        <v>-10.84833377385097</v>
+        <v>-8.783877045449774</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.279012611071177</v>
       </c>
       <c r="E67">
-        <v>-11.6536270874277</v>
+        <v>-7.498895687254268</v>
       </c>
       <c r="F67">
-        <v>4.433578753974575</v>
+        <v>5.635652513403439</v>
       </c>
       <c r="G67">
-        <v>-10.34397185852757</v>
+        <v>-8.451148090290751</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.529607115318267</v>
       </c>
       <c r="E68">
-        <v>-10.21002897587584</v>
+        <v>-6.942008193553307</v>
       </c>
       <c r="F68">
-        <v>4.564742448533849</v>
+        <v>5.898546505825501</v>
       </c>
       <c r="G68">
-        <v>-9.994902252972764</v>
+        <v>-8.458424235466182</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.76132137963174</v>
       </c>
       <c r="E69">
-        <v>-10.65303126183868</v>
+        <v>-7.070857421694789</v>
       </c>
       <c r="F69">
-        <v>4.720495401077823</v>
+        <v>5.697485169818005</v>
       </c>
       <c r="G69">
-        <v>-10.85342733654823</v>
+        <v>-8.521475022713865</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.985145149921753</v>
       </c>
       <c r="E70">
-        <v>-12.33816768440859</v>
+        <v>-7.07673421571942</v>
       </c>
       <c r="F70">
-        <v>4.331701160573876</v>
+        <v>5.953788671183394</v>
       </c>
       <c r="G70">
-        <v>-11.60868050170532</v>
+        <v>-7.920854954316115</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.200712007847184</v>
       </c>
       <c r="E71">
-        <v>-9.955648935441419</v>
+        <v>-7.162061942388023</v>
       </c>
       <c r="F71">
-        <v>3.955090547830303</v>
+        <v>5.773877211704176</v>
       </c>
       <c r="G71">
-        <v>-11.26133137683607</v>
+        <v>-8.668318962985623</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.414245270387104</v>
       </c>
       <c r="E72">
-        <v>-10.51150643273382</v>
+        <v>-6.604846344992402</v>
       </c>
       <c r="F72">
-        <v>5.004545896967385</v>
+        <v>5.805290560353138</v>
       </c>
       <c r="G72">
-        <v>-10.32540685374016</v>
+        <v>-8.446546652948912</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.633358916555258</v>
       </c>
       <c r="E73">
-        <v>-9.699599304054415</v>
+        <v>-7.67261205733787</v>
       </c>
       <c r="F73">
-        <v>4.237749386483161</v>
+        <v>5.677766712161765</v>
       </c>
       <c r="G73">
-        <v>-10.87489679469325</v>
+        <v>-8.501608561747787</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.856229297629792</v>
       </c>
       <c r="E74">
-        <v>-11.4180527878721</v>
+        <v>-7.055885094868781</v>
       </c>
       <c r="F74">
-        <v>4.190345233490556</v>
+        <v>5.911522052822953</v>
       </c>
       <c r="G74">
-        <v>-10.93529114931948</v>
+        <v>-8.491925310059349</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.09391109822656</v>
       </c>
       <c r="E75">
-        <v>-11.82953635309081</v>
+        <v>-7.217698361295426</v>
       </c>
       <c r="F75">
-        <v>4.048997590081266</v>
+        <v>5.867428055971935</v>
       </c>
       <c r="G75">
-        <v>-10.76747118163042</v>
+        <v>-8.629927963773302</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.33314861010579</v>
       </c>
       <c r="E76">
-        <v>-11.58222092511992</v>
+        <v>-7.57901944013286</v>
       </c>
       <c r="F76">
-        <v>4.518920477280592</v>
+        <v>5.708638308529298</v>
       </c>
       <c r="G76">
-        <v>-10.95988827948465</v>
+        <v>-8.772769632586883</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.58451129184163</v>
       </c>
       <c r="E77">
-        <v>-12.18408769746877</v>
+        <v>-8.214793029737613</v>
       </c>
       <c r="F77">
-        <v>4.172167539203524</v>
+        <v>5.809907880256342</v>
       </c>
       <c r="G77">
-        <v>-10.33463322512515</v>
+        <v>-8.072208955869021</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.83049672189571</v>
       </c>
       <c r="E78">
-        <v>-13.61062857010955</v>
+        <v>-7.768796278409575</v>
       </c>
       <c r="F78">
-        <v>4.413467650169409</v>
+        <v>5.771746650744175</v>
       </c>
       <c r="G78">
-        <v>-10.7976774965496</v>
+        <v>-7.897004497104</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.07210925161657</v>
       </c>
       <c r="E79">
-        <v>-12.89236389717106</v>
+        <v>-9.231794040059702</v>
       </c>
       <c r="F79">
-        <v>4.590075580446263</v>
+        <v>5.628087862281074</v>
       </c>
       <c r="G79">
-        <v>-10.76899324572704</v>
+        <v>-8.255240426918201</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.29195849477388</v>
       </c>
       <c r="E80">
-        <v>-15.21526329757031</v>
+        <v>-9.457118214065625</v>
       </c>
       <c r="F80">
-        <v>4.49147832196065</v>
+        <v>5.8569724026138</v>
       </c>
       <c r="G80">
-        <v>-11.20338198451942</v>
+        <v>-8.042255883175178</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.4774239227913</v>
       </c>
       <c r="E81">
-        <v>-14.26336802797623</v>
+        <v>-9.947645697218475</v>
       </c>
       <c r="F81">
-        <v>3.692426841546219</v>
+        <v>5.935647425062085</v>
       </c>
       <c r="G81">
-        <v>-10.64914440452739</v>
+        <v>-8.004428804794538</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.61286877157942</v>
       </c>
       <c r="E82">
-        <v>-16.36085188372042</v>
+        <v>-10.7039537858924</v>
       </c>
       <c r="F82">
-        <v>4.645162012732431</v>
+        <v>5.83260846056266</v>
       </c>
       <c r="G82">
-        <v>-9.361295426666299</v>
+        <v>-8.267218523102228</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.67528999562846</v>
       </c>
       <c r="E83">
-        <v>-16.29013515449256</v>
+        <v>-11.82717317584698</v>
       </c>
       <c r="F83">
-        <v>4.257802504570131</v>
+        <v>5.492860197243665</v>
       </c>
       <c r="G83">
-        <v>-10.19688511900883</v>
+        <v>-8.032449926490957</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.65378845485456</v>
       </c>
       <c r="E84">
-        <v>-17.43948655010296</v>
+        <v>-12.34981328896341</v>
       </c>
       <c r="F84">
-        <v>4.850524232295262</v>
+        <v>5.631475884958523</v>
       </c>
       <c r="G84">
-        <v>-10.25697662726249</v>
+        <v>-7.894032164387017</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.52153374423879</v>
       </c>
       <c r="E85">
-        <v>-17.29643749244189</v>
+        <v>-13.52645543618925</v>
       </c>
       <c r="F85">
-        <v>4.421234422938057</v>
+        <v>5.69921480095505</v>
       </c>
       <c r="G85">
-        <v>-9.917442766326729</v>
+        <v>-8.082971750445886</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.27587910284046</v>
       </c>
       <c r="E86">
-        <v>-19.14167190516129</v>
+        <v>-13.90358363732899</v>
       </c>
       <c r="F86">
-        <v>4.038999195529476</v>
+        <v>5.527422998758072</v>
       </c>
       <c r="G86">
-        <v>-9.750701036153801</v>
+        <v>-7.822851518482609</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.89923340446731</v>
       </c>
       <c r="E87">
-        <v>-19.79243858764868</v>
+        <v>-15.41094600235093</v>
       </c>
       <c r="F87">
-        <v>4.176229852946853</v>
+        <v>5.613241861688101</v>
       </c>
       <c r="G87">
-        <v>-8.907151183552962</v>
+        <v>-7.251839904492676</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.39967114717036</v>
       </c>
       <c r="E88">
-        <v>-21.13545422733583</v>
+        <v>-17.53866938975119</v>
       </c>
       <c r="F88">
-        <v>4.357431908839634</v>
+        <v>5.746516236389708</v>
       </c>
       <c r="G88">
-        <v>-10.04110068388481</v>
+        <v>-7.614866550631569</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.782175431535151</v>
       </c>
       <c r="E89">
-        <v>-23.39706053500326</v>
+        <v>-19.08493488525281</v>
       </c>
       <c r="F89">
-        <v>4.391325389492578</v>
+        <v>5.225153390211339</v>
       </c>
       <c r="G89">
-        <v>-8.792923275457982</v>
+        <v>-7.248184862065117</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.067662135780742</v>
       </c>
       <c r="E90">
-        <v>-24.56591956420639</v>
+        <v>-20.44873734762073</v>
       </c>
       <c r="F90">
-        <v>4.369315667600195</v>
+        <v>5.476963826783943</v>
       </c>
       <c r="G90">
-        <v>-8.760689717363801</v>
+        <v>-7.36950094172497</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.283663109872956</v>
       </c>
       <c r="E91">
-        <v>-26.52805441608573</v>
+        <v>-21.83535755300726</v>
       </c>
       <c r="F91">
-        <v>3.913766611574247</v>
+        <v>5.656870316058745</v>
       </c>
       <c r="G91">
-        <v>-9.113531848852762</v>
+        <v>-6.778149016625672</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.457873373843209</v>
       </c>
       <c r="E92">
-        <v>-27.39339260845906</v>
+        <v>-23.76133870030397</v>
       </c>
       <c r="F92">
-        <v>3.83630763247327</v>
+        <v>5.256795368263473</v>
       </c>
       <c r="G92">
-        <v>-9.069731386847655</v>
+        <v>-6.869997622085629</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.628218124094203</v>
       </c>
       <c r="E93">
-        <v>-28.8032666440533</v>
+        <v>-25.5532168071333</v>
       </c>
       <c r="F93">
-        <v>3.695276425411849</v>
+        <v>4.99802001856813</v>
       </c>
       <c r="G93">
-        <v>-8.06736471928021</v>
+        <v>-6.639132088638072</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.816876036866369</v>
       </c>
       <c r="E94">
-        <v>-29.92308040072152</v>
+        <v>-27.78496567858654</v>
       </c>
       <c r="F94">
-        <v>3.726673206712756</v>
+        <v>5.087901195241488</v>
       </c>
       <c r="G94">
-        <v>-8.938525806676665</v>
+        <v>-6.219188599668318</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.055781835443968</v>
       </c>
       <c r="E95">
-        <v>-35.42209417003618</v>
+        <v>-29.73020526679649</v>
       </c>
       <c r="F95">
-        <v>4.092861300794305</v>
+        <v>4.841687208842196</v>
       </c>
       <c r="G95">
-        <v>-8.477587100764955</v>
+        <v>-6.971145699779131</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.347913146005614</v>
       </c>
       <c r="E96">
-        <v>-36.60151066242702</v>
+        <v>-33.03026184467308</v>
       </c>
       <c r="F96">
-        <v>3.48963090419726</v>
+        <v>4.632600649436379</v>
       </c>
       <c r="G96">
-        <v>-8.036854252616164</v>
+        <v>-7.358180753177902</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.706632496916466</v>
       </c>
       <c r="E97">
-        <v>-38.41781795826898</v>
+        <v>-35.25707047125545</v>
       </c>
       <c r="F97">
-        <v>3.664225901685312</v>
+        <v>4.060661003112683</v>
       </c>
       <c r="G97">
-        <v>-8.208061661412192</v>
+        <v>-7.12066565325678</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.115503915891542</v>
       </c>
       <c r="E98">
-        <v>-39.52884974959085</v>
+        <v>-37.88676759221978</v>
       </c>
       <c r="F98">
-        <v>3.377194939880478</v>
+        <v>4.014790986550063</v>
       </c>
       <c r="G98">
-        <v>-7.499380263643673</v>
+        <v>-6.956402825073114</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.572739014937206</v>
       </c>
       <c r="E99">
-        <v>-43.92159130776189</v>
+        <v>-39.89962146079793</v>
       </c>
       <c r="F99">
-        <v>2.861012703439216</v>
+        <v>3.839095917151093</v>
       </c>
       <c r="G99">
-        <v>-9.340057019417593</v>
+        <v>-6.969986529180677</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.049733259670089</v>
       </c>
       <c r="E100">
-        <v>-44.83721658285624</v>
+        <v>-43.7808805080767</v>
       </c>
       <c r="F100">
-        <v>2.961745493089247</v>
+        <v>3.750904609979447</v>
       </c>
       <c r="G100">
-        <v>-8.526315343185788</v>
+        <v>-7.352369235718084</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.556054910606965</v>
       </c>
       <c r="E101">
-        <v>-47.23084413381449</v>
+        <v>-45.3917948910606</v>
       </c>
       <c r="F101">
-        <v>2.290169815556827</v>
+        <v>3.198898796836718</v>
       </c>
       <c r="G101">
-        <v>-8.977207903910895</v>
+        <v>-6.679131306518519</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.050014920306602</v>
       </c>
       <c r="E102">
-        <v>-49.10570444121672</v>
+        <v>-47.58893089933272</v>
       </c>
       <c r="F102">
-        <v>2.624114536851808</v>
+        <v>2.791373512620667</v>
       </c>
       <c r="G102">
-        <v>-8.995466146208846</v>
+        <v>-6.584671956467449</v>
       </c>
     </row>
   </sheetData>
